--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260615.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,726,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>1,726,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>938,659</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>938,659</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>7,349,249</t>
+          <t>2,575,703</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,575,703</t>
+          <t>3,351,981</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,351,981</t>
+          <t>7,349,249</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,187,076</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>828,000</t>
+          <t>1,187,076</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>828,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>202606WVHFM6F</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>202606WVHFM6F</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
